--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:44</t>
+    <t xml:space="preserve">2026-09-10 00:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:53</t>
+    <t xml:space="preserve">2026-09-18 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:02</t>
+    <t xml:space="preserve">2026-09-23 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:23</t>
+    <t xml:space="preserve">2026-10-02 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2019_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:37</t>
+    <t xml:space="preserve">2026-10-05 14:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
